--- a/test/fixtures/xlsx/matrix/matrix.xlsx
+++ b/test/fixtures/xlsx/matrix/matrix.xlsx
@@ -421,7 +421,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>:enum Element</t>
+          <t>:enum Affinity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>defender Element</t>
+          <t>defender Affinity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
